--- a/基本設計/21_ログファイルRedisセキュリティ_基本設計書.xlsx
+++ b/基本設計/21_ログファイルRedisセキュリティ_基本設計書.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R8178837c788a4f62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rdead3f514ac34f81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_操作ログ" sheetId="34" r:id="R6b3fa3fd470d46b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_ファイル管理" sheetId="35" r:id="Ra9e8e18f9b334be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_Redis" sheetId="36" r:id="R2ce0720c4b4c4c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_セキュリティ" sheetId="37" r:id="Rb3549d52e94a4aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re8bfc49f9f1e4c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R2061f1e32d8d4110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_操作ログ" sheetId="34" r:id="R774d7fe07a584a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_ファイル管理" sheetId="35" r:id="R448b33139b3343f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_Redis" sheetId="36" r:id="R6352ec7f92e1402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_セキュリティ" sheetId="37" r:id="R1a81201f6ca744d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1102,10 +1102,7 @@
       <x:c r="F16" s="140"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1120,25 +1117,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="182" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="182"/>
-      <x:c r="D19" s="182"/>
-      <x:c r="E19" s="182"/>
-      <x:c r="F19" s="182"/>
-      <x:c r="G19" s="182"/>
-      <x:c r="H19" s="182"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="182"/>
-      <x:c r="C20" s="182"/>
-      <x:c r="D20" s="182"/>
-      <x:c r="E20" s="182"/>
-      <x:c r="F20" s="182"/>
-      <x:c r="G20" s="182"/>
-      <x:c r="H20" s="182"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="182"/>
